--- a/data/trans_orig/IQ3005_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer huevo</t>
+          <t>Menores según la edad en meses en la que empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,21; 12,0</t>
+          <t>10,18; 12,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 11,61</t>
+          <t>10,15; 11,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 16,1</t>
+          <t>8,47; 16,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 12,94</t>
+          <t>9,59; 12,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 15,41</t>
+          <t>11,18; 15,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 12,17</t>
+          <t>10,24; 12,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 13,53</t>
+          <t>10,94; 13,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 14,68</t>
+          <t>8,84; 14,55</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,05; 12,92</t>
+          <t>11,09; 12,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 11,63</t>
+          <t>10,5; 11,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 10,2</t>
+          <t>8,89; 10,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 11,56</t>
+          <t>10,13; 11,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,59; 11,72</t>
+          <t>10,58; 11,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,21</t>
+          <t>8,59; 10,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,75; 11,91</t>
+          <t>10,79; 11,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 11,48</t>
+          <t>10,67; 11,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 10,01</t>
+          <t>8,86; 9,96</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 10,9</t>
+          <t>8,01; 11,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 15,03</t>
+          <t>10,67; 15,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 11,05</t>
+          <t>8,71; 10,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,28; 13,33</t>
+          <t>11,38; 13,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 11,37</t>
+          <t>9,83; 11,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 10,59</t>
+          <t>8,03; 10,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 11,79</t>
+          <t>10,08; 11,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,57; 12,9</t>
+          <t>10,5; 12,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,37</t>
+          <t>8,71; 10,43</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 11,95</t>
+          <t>10,46; 11,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 11,99</t>
+          <t>10,76; 12,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 10,46</t>
+          <t>9,14; 10,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,81</t>
+          <t>10,74; 11,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,63</t>
+          <t>10,68; 11,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 9,99</t>
+          <t>8,7; 9,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 11,69</t>
+          <t>10,74; 11,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 11,62</t>
+          <t>10,9; 11,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,94</t>
+          <t>9,05; 9,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Estudios-trans_orig.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 12,0</t>
+          <t>10,16; 12,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 11,6</t>
+          <t>10,16; 11,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 12,84</t>
+          <t>9,59; 12,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 15,83</t>
+          <t>11,18; 15,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 12,34</t>
+          <t>10,18; 12,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,94; 13,18</t>
+          <t>10,91; 13,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 14,55</t>
+          <t>8,93; 14,17</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,09; 12,9</t>
+          <t>11,12; 12,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 11,61</t>
+          <t>10,5; 11,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 10,29</t>
+          <t>8,9; 10,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 11,6</t>
+          <t>10,1; 11,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,58; 11,71</t>
+          <t>10,56; 11,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 10,23</t>
+          <t>8,55; 10,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,79; 11,99</t>
+          <t>10,78; 11,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,67; 11,52</t>
+          <t>10,67; 11,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 9,96</t>
+          <t>8,96; 9,99</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 11,0</t>
+          <t>7,76; 10,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,67; 15,11</t>
+          <t>10,73; 14,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 10,96</t>
+          <t>8,72; 10,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 13,16</t>
+          <t>11,36; 13,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 11,41</t>
+          <t>9,78; 11,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,62</t>
+          <t>7,95; 10,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,86</t>
+          <t>10,01; 11,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 12,58</t>
+          <t>10,61; 12,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 10,43</t>
+          <t>8,66; 10,4</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,95</t>
+          <t>10,38; 11,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 12,13</t>
+          <t>10,8; 12,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 10,35</t>
+          <t>9,12; 10,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 11,82</t>
+          <t>10,73; 11,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,68</t>
+          <t>10,69; 11,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 9,99</t>
+          <t>8,73; 10,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 11,72</t>
+          <t>10,78; 11,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 11,72</t>
+          <t>10,86; 11,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,99</t>
+          <t>9,11; 9,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Estudios-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,03</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>10,96</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,55</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,16; 12,0</t>
+          <t>9,6; 12,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,16; 11,58</t>
+          <t>11,17; 15,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 16,1</t>
+          <t>6,0; 12,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 12,99</t>
+          <t>10,21; 12,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 15,86</t>
+          <t>10,09; 11,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 12,0</t>
+          <t>8,31; 16,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 12,2</t>
+          <t>10,13; 12,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 13,37</t>
+          <t>10,99; 13,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 14,17</t>
+          <t>8,77; 14,68</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,15</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,38</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>11,96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>11,04</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,51</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,92</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,15</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,38</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,12; 12,97</t>
+          <t>10,03; 11,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 11,68</t>
+          <t>10,59; 11,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 10,33</t>
+          <t>8,51; 10,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,1; 11,61</t>
+          <t>11,05; 12,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 11,68</t>
+          <t>10,53; 11,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,55; 10,19</t>
+          <t>8,79; 10,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,78; 11,96</t>
+          <t>10,75; 11,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,67; 11,5</t>
+          <t>10,69; 11,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,99</t>
+          <t>8,97; 10,01</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,65</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,21</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>9,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>12,17</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,8</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,65</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,76; 10,89</t>
+          <t>11,28; 13,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,73; 14,93</t>
+          <t>9,7; 11,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 10,94</t>
+          <t>8,0; 10,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 13,28</t>
+          <t>7,93; 10,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 11,44</t>
+          <t>10,8; 15,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 10,54</t>
+          <t>8,69; 11,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 11,78</t>
+          <t>10,06; 11,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 12,86</t>
+          <t>10,57; 12,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,66; 10,4</t>
+          <t>8,63; 10,37</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>11,21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>11,3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,71</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 11,96</t>
+          <t>10,7; 11,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 12,08</t>
+          <t>10,68; 11,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,12; 10,29</t>
+          <t>8,71; 9,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,73; 11,82</t>
+          <t>10,37; 11,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 11,62</t>
+          <t>10,8; 11,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 10,02</t>
+          <t>9,18; 10,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 11,66</t>
+          <t>10,78; 11,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,86; 11,66</t>
+          <t>10,87; 11,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,98</t>
+          <t>9,06; 9,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10,66</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12,55</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10,03</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,96</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,58</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,04</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11,64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10,93</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>10.66032208056085</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>12.55386241705082</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10.03263922865588</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>11.60283839969825</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>10.95619923328455</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>11.5797210845842</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>11.03795043556018</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>11.64346587316608</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>10.93173262746863</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>9,6; 12,94</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11,17; 15,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,0; 12,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10,21; 12,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,09; 11,61</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,31; 16,1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,13; 12,17</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10,99; 13,53</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8,77; 14,68</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>9.595413080522</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>11.17204372839858</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6.000162010211073</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>10.21380611483802</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>10.09200883104265</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>8.309066811731164</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>10.13278266757921</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>10.99391745385101</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>8.769128767976532</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.9396688086955</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15.41411432954116</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>11.60505487709037</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>16.09504697404877</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>12.17154726728251</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>13.52667594352587</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>14.67744201871838</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10,92</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11,15</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,38</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,96</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,04</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,37</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11,09</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>10,03; 11,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10,59; 11,72</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8,51; 10,21</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11,05; 12,92</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,53; 11,63</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,79; 10,2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,75; 11,91</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10,69; 11,48</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8,97; 10,01</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>10.91935730386783</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>11.14639429238724</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>9.380290537907024</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>11.95632403594334</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>11.03627982142649</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>9.506838816558425</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>11.37195186597921</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>11.09077493732383</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>9.444917718966307</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12,17</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,21</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,85</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,17</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,06</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11,36</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9,47</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>10.02637148144957</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>10.59207205892121</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>8.510331825156351</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>11.04537397601009</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>10.52826655670332</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>8.788534070276679</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>10.75081485909936</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>10.68929870127627</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>8.965926052391904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11,28; 13,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,7; 11,37</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8,0; 10,59</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>7,93; 10,9</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>10,8; 15,03</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8,69; 11,05</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,06; 11,79</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10,57; 12,9</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>8,63; 10,37</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11.55826423945998</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>11.72046376978217</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10.20700285226178</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>12.92345575911595</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>11.6260069896278</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>10.20458563624246</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>11.91297124631221</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>11.48454589294276</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>10.00851446712105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,107 +845,215 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,21</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,24</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11,22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>12.17337098970697</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>10.65116226500947</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.205155504807566</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>9.845586497082577</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>12.17276770047756</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>9.801000309967604</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>11.06409235771775</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>11.36378554965343</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9.470500568482187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10,7; 11,81</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10,68; 11,63</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,71; 9,99</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10,37; 11,95</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,8; 11,99</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,18; 10,46</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,78; 11,69</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10,87; 11,62</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9,06; 9,94</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>11.28000082211598</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>9.700421604641328</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>7.998091380420074</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>7.927684795962963</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>10.79583029826833</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>8.692297286987252</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>10.06203131691409</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>10.56586604154866</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>8.62740684546935</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13.33316277695473</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.36700054191453</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.58840658401586</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.89627644616221</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>15.02663084213839</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>11.04841312907816</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>11.78949042083269</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>12.89847117328682</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>10.37263376642088</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>11.27607875236186</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>11.14422777139552</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>9.34668281645331</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>11.20630757442294</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>11.30324518534518</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>9.7089233786826</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>11.24494020283545</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>11.22417108368449</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>9.525522734041665</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>10.70090000564307</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>10.67999182304633</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>8.71068908156084</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>10.37498581962022</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>10.80123575423183</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>9.18391918169867</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>10.78232539958185</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>10.87275952914075</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>9.062670232824527</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11.81386257715074</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>11.62985829075116</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.985202220271852</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>11.94753713746618</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>11.99059437484276</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>10.45868568067961</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>11.69476470830229</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>11.62135942144971</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>9.939004192378006</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1061,13 +1062,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
